--- a/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:43:57+00:00</t>
+    <t>2026-09-02T12:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>Media.subject</t>
+  </si>
+  <si>
+    <t>FRPatientINSDocument / FRSpecimenDocument</t>
   </si>
   <si>
     <t>FRLMObservationMedia.note</t>
@@ -637,7 +640,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -739,46 +742,35 @@
       <c r="D7" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:54:48+00:00</t>
+    <t>2026-09-02T15:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:48:56+00:00</t>
+    <t>2026-09-03T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:02:14+00:00</t>
+    <t>2026-09-03T10:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRMediaLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:35:28+00:00</t>
+    <t>2026-09-04T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
